--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/69.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/69.xlsx
@@ -426,13 +426,13 @@
         <v>-15.14380441283523</v>
       </c>
       <c r="E2">
-        <v>-17.08183623867092</v>
+        <v>-18.24392418157127</v>
       </c>
       <c r="F2">
-        <v>3.653435587896446</v>
+        <v>3.398754029905738</v>
       </c>
       <c r="G2">
-        <v>-10.56343889547398</v>
+        <v>-11.25942864411247</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.55647046610462</v>
       </c>
       <c r="E3">
-        <v>-16.99632053551007</v>
+        <v>-18.55479486524982</v>
       </c>
       <c r="F3">
-        <v>3.931617929104576</v>
+        <v>3.612838958220048</v>
       </c>
       <c r="G3">
-        <v>-10.99839762539397</v>
+        <v>-11.40970202909192</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.90155612086746</v>
       </c>
       <c r="E4">
-        <v>-17.13481938456066</v>
+        <v>-18.24079047755796</v>
       </c>
       <c r="F4">
-        <v>4.282875529118067</v>
+        <v>3.713018398445008</v>
       </c>
       <c r="G4">
-        <v>-10.83605590751888</v>
+        <v>-11.70784366364775</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.23008887149455</v>
       </c>
       <c r="E5">
-        <v>-17.88048697161168</v>
+        <v>-19.66764018179077</v>
       </c>
       <c r="F5">
-        <v>4.098431243210729</v>
+        <v>3.601566534602752</v>
       </c>
       <c r="G5">
-        <v>-10.37046697434147</v>
+        <v>-10.53976488192258</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.54369133648426</v>
       </c>
       <c r="E6">
-        <v>-19.16560449635242</v>
+        <v>-19.35767972138776</v>
       </c>
       <c r="F6">
-        <v>4.039587336385464</v>
+        <v>3.784077410991956</v>
       </c>
       <c r="G6">
-        <v>-10.4490259809177</v>
+        <v>-12.05189615026332</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.85697605592775</v>
       </c>
       <c r="E7">
-        <v>-19.17382820515035</v>
+        <v>-20.31656597861592</v>
       </c>
       <c r="F7">
-        <v>3.618292929200079</v>
+        <v>3.722501548472257</v>
       </c>
       <c r="G7">
-        <v>-10.01819502771949</v>
+        <v>-10.0211710956739</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.18127478609192</v>
       </c>
       <c r="E8">
-        <v>-20.07499906115076</v>
+        <v>-21.77960271864402</v>
       </c>
       <c r="F8">
-        <v>4.092758583236358</v>
+        <v>3.740563271322898</v>
       </c>
       <c r="G8">
-        <v>-10.05216223330286</v>
+        <v>-10.90878418338397</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.53201660251408</v>
       </c>
       <c r="E9">
-        <v>-21.32737571881604</v>
+        <v>-22.24449586027146</v>
       </c>
       <c r="F9">
-        <v>3.761259202514441</v>
+        <v>3.979446206207414</v>
       </c>
       <c r="G9">
-        <v>-8.964276506490522</v>
+        <v>-10.42431838257508</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.913228966025612</v>
       </c>
       <c r="E10">
-        <v>-21.62884529045467</v>
+        <v>-22.15921110928501</v>
       </c>
       <c r="F10">
-        <v>3.84044118581324</v>
+        <v>4.339595501922554</v>
       </c>
       <c r="G10">
-        <v>-8.427829593736906</v>
+        <v>-10.70455767230257</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.338438101292164</v>
       </c>
       <c r="E11">
-        <v>-21.7451682022897</v>
+        <v>-23.167589058943</v>
       </c>
       <c r="F11">
-        <v>3.89216113297443</v>
+        <v>3.826082265253113</v>
       </c>
       <c r="G11">
-        <v>-7.724703188206617</v>
+        <v>-10.87379651789561</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.818482550285577</v>
       </c>
       <c r="E12">
-        <v>-23.49888768887016</v>
+        <v>-25.48687419281542</v>
       </c>
       <c r="F12">
-        <v>3.744811139364454</v>
+        <v>4.055664290938996</v>
       </c>
       <c r="G12">
-        <v>-7.256997867123367</v>
+        <v>-9.064941102712726</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.36127598476302</v>
       </c>
       <c r="E13">
-        <v>-24.66578487116666</v>
+        <v>-25.74099404022985</v>
       </c>
       <c r="F13">
-        <v>4.44538630293408</v>
+        <v>3.575931876955718</v>
       </c>
       <c r="G13">
-        <v>-7.072642433805965</v>
+        <v>-8.335167896898188</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.988803775615454</v>
       </c>
       <c r="E14">
-        <v>-25.32885309231777</v>
+        <v>-25.85426023210971</v>
       </c>
       <c r="F14">
-        <v>4.635937313334855</v>
+        <v>4.4826164474855</v>
       </c>
       <c r="G14">
-        <v>-6.696076322757852</v>
+        <v>-7.468485721515817</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.708766838036719</v>
       </c>
       <c r="E15">
-        <v>-25.04596384953261</v>
+        <v>-27.71353391933495</v>
       </c>
       <c r="F15">
-        <v>4.91203216868793</v>
+        <v>4.936563440954435</v>
       </c>
       <c r="G15">
-        <v>-5.941257552780071</v>
+        <v>-6.666102363812325</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.52631848408208</v>
       </c>
       <c r="E16">
-        <v>-26.6714731800079</v>
+        <v>-27.23385531007247</v>
       </c>
       <c r="F16">
-        <v>4.780608366764178</v>
+        <v>4.364042280713973</v>
       </c>
       <c r="G16">
-        <v>-5.449310566815644</v>
+        <v>-6.511392767284507</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.444989892832296</v>
       </c>
       <c r="E17">
-        <v>-27.01293823408228</v>
+        <v>-28.18177360325406</v>
       </c>
       <c r="F17">
-        <v>4.839326361744218</v>
+        <v>4.790918227459421</v>
       </c>
       <c r="G17">
-        <v>-5.497505149080768</v>
+        <v>-7.706708969174622</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.460287703254524</v>
       </c>
       <c r="E18">
-        <v>-29.10212254667696</v>
+        <v>-30.23505390967892</v>
       </c>
       <c r="F18">
-        <v>5.23976247772711</v>
+        <v>5.829949401199674</v>
       </c>
       <c r="G18">
-        <v>-5.132105034999444</v>
+        <v>-6.659530077028757</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-7.566028105868721</v>
       </c>
       <c r="E19">
-        <v>-28.70397458344857</v>
+        <v>-30.10672601324956</v>
       </c>
       <c r="F19">
-        <v>5.164531806939665</v>
+        <v>4.970239889347846</v>
       </c>
       <c r="G19">
-        <v>-4.440961650604248</v>
+        <v>-5.454908330796057</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-7.755008218040922</v>
       </c>
       <c r="E20">
-        <v>-29.94839697651938</v>
+        <v>-28.47425415398747</v>
       </c>
       <c r="F20">
-        <v>5.464366015322168</v>
+        <v>5.192446131679202</v>
       </c>
       <c r="G20">
-        <v>-3.468509298253176</v>
+        <v>-6.600845429438088</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.007049004974919</v>
       </c>
       <c r="E21">
-        <v>-30.47464188400274</v>
+        <v>-30.80347249559571</v>
       </c>
       <c r="F21">
-        <v>5.565534526226072</v>
+        <v>6.12392870877919</v>
       </c>
       <c r="G21">
-        <v>-3.979940177837587</v>
+        <v>-5.123774013460014</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.310018463786271</v>
       </c>
       <c r="E22">
-        <v>-31.58599280412115</v>
+        <v>-32.56275294825759</v>
       </c>
       <c r="F22">
-        <v>5.685008299997039</v>
+        <v>5.418414818754074</v>
       </c>
       <c r="G22">
-        <v>-2.888523856627288</v>
+        <v>-4.290038583756028</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.648370041802236</v>
       </c>
       <c r="E23">
-        <v>-31.90298372042107</v>
+        <v>-32.45387258345417</v>
       </c>
       <c r="F23">
-        <v>5.381953399152451</v>
+        <v>5.992050961518704</v>
       </c>
       <c r="G23">
-        <v>-2.980276655094041</v>
+        <v>-5.540010093161815</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.004551176907514</v>
       </c>
       <c r="E24">
-        <v>-32.84430176273648</v>
+        <v>-33.89417411972676</v>
       </c>
       <c r="F24">
-        <v>5.981739444088656</v>
+        <v>6.087314869575453</v>
       </c>
       <c r="G24">
-        <v>-2.516685985846335</v>
+        <v>-4.962649628783482</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.36775320056725</v>
       </c>
       <c r="E25">
-        <v>-33.25381166725011</v>
+        <v>-32.39944938282999</v>
       </c>
       <c r="F25">
-        <v>5.977990253223584</v>
+        <v>5.810636843570807</v>
       </c>
       <c r="G25">
-        <v>-2.018110932331829</v>
+        <v>-5.133447054617258</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.723652782058153</v>
       </c>
       <c r="E26">
-        <v>-33.5134539887169</v>
+        <v>-34.71851714995004</v>
       </c>
       <c r="F26">
-        <v>5.623119314599082</v>
+        <v>6.192539067283462</v>
       </c>
       <c r="G26">
-        <v>-1.447431035048526</v>
+        <v>-5.342411649630495</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.05690304945927</v>
       </c>
       <c r="E27">
-        <v>-32.84433119781753</v>
+        <v>-32.14766622800352</v>
       </c>
       <c r="F27">
-        <v>5.935534767095304</v>
+        <v>5.927005896316081</v>
       </c>
       <c r="G27">
-        <v>-2.232965320044269</v>
+        <v>-3.276820334750417</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.36034585040448</v>
       </c>
       <c r="E28">
-        <v>-32.93618223611511</v>
+        <v>-34.35809816791656</v>
       </c>
       <c r="F28">
-        <v>6.145506022887312</v>
+        <v>6.268765435689073</v>
       </c>
       <c r="G28">
-        <v>-1.862019941527484</v>
+        <v>-3.937179298474903</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.6247671867694</v>
       </c>
       <c r="E29">
-        <v>-33.87462922590966</v>
+        <v>-33.92360467230261</v>
       </c>
       <c r="F29">
-        <v>6.25122392756739</v>
+        <v>6.529366507140186</v>
       </c>
       <c r="G29">
-        <v>-1.026105780708027</v>
+        <v>-4.489924038714282</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.84168592383592</v>
       </c>
       <c r="E30">
-        <v>-32.42102303300253</v>
+        <v>-34.65690273260168</v>
       </c>
       <c r="F30">
-        <v>6.30897107595135</v>
+        <v>6.263319748383069</v>
       </c>
       <c r="G30">
-        <v>-2.255284189091612</v>
+        <v>-4.245797873470035</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.00915871791008</v>
       </c>
       <c r="E31">
-        <v>-32.92788607173306</v>
+        <v>-35.21569831125217</v>
       </c>
       <c r="F31">
-        <v>6.028726099910249</v>
+        <v>5.065793725995575</v>
       </c>
       <c r="G31">
-        <v>-1.482421981758444</v>
+        <v>-4.568778355230857</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.11927676292957</v>
       </c>
       <c r="E32">
-        <v>-34.01354469456895</v>
+        <v>-34.73249202073771</v>
       </c>
       <c r="F32">
-        <v>5.663290163430442</v>
+        <v>5.51652168373723</v>
       </c>
       <c r="G32">
-        <v>-1.86836582402345</v>
+        <v>-4.165988721479661</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.17106291742492</v>
       </c>
       <c r="E33">
-        <v>-33.33664198532441</v>
+        <v>-33.49583596059006</v>
       </c>
       <c r="F33">
-        <v>5.804049665983745</v>
+        <v>6.179606595390957</v>
       </c>
       <c r="G33">
-        <v>-1.790686184825156</v>
+        <v>-5.193283410975291</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.16655260087956</v>
       </c>
       <c r="E34">
-        <v>-33.26387167225815</v>
+        <v>-31.47885363757368</v>
       </c>
       <c r="F34">
-        <v>5.504391071490635</v>
+        <v>5.711443160555176</v>
       </c>
       <c r="G34">
-        <v>-2.259441496807428</v>
+        <v>-4.640010394064842</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.10698170113406</v>
       </c>
       <c r="E35">
-        <v>-32.97323194620886</v>
+        <v>-32.53293068268008</v>
       </c>
       <c r="F35">
-        <v>6.034461715807232</v>
+        <v>6.122288541321647</v>
       </c>
       <c r="G35">
-        <v>-2.934477364567311</v>
+        <v>-5.086115433622267</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.00001720504839</v>
       </c>
       <c r="E36">
-        <v>-31.24714520802321</v>
+        <v>-30.78313738306427</v>
       </c>
       <c r="F36">
-        <v>5.614161349505208</v>
+        <v>4.886322957974645</v>
       </c>
       <c r="G36">
-        <v>-1.971442118091847</v>
+        <v>-5.023844410867126</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.85456782845964</v>
       </c>
       <c r="E37">
-        <v>-30.93483446961021</v>
+        <v>-32.19620920512874</v>
       </c>
       <c r="F37">
-        <v>6.195942000574163</v>
+        <v>5.722722211111694</v>
       </c>
       <c r="G37">
-        <v>-2.602768833458367</v>
+        <v>-5.355008259197203</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.67424846568896</v>
       </c>
       <c r="E38">
-        <v>-30.58666274553048</v>
+        <v>-32.497463674252</v>
       </c>
       <c r="F38">
-        <v>5.961620056609461</v>
+        <v>5.538511524811947</v>
       </c>
       <c r="G38">
-        <v>-3.564944399885257</v>
+        <v>-4.159501746456639</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.47091114713625</v>
       </c>
       <c r="E39">
-        <v>-31.83859787698001</v>
+        <v>-32.59492322760808</v>
       </c>
       <c r="F39">
-        <v>6.469782039856818</v>
+        <v>6.177658275259572</v>
       </c>
       <c r="G39">
-        <v>-3.19897663447415</v>
+        <v>-5.915358871011374</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.25414288180956</v>
       </c>
       <c r="E40">
-        <v>-28.81595016023623</v>
+        <v>-31.06116530900219</v>
       </c>
       <c r="F40">
-        <v>6.402608070429</v>
+        <v>6.074730311992123</v>
       </c>
       <c r="G40">
-        <v>-3.268650093067399</v>
+        <v>-5.339773547496701</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.02989897594892</v>
       </c>
       <c r="E41">
-        <v>-31.12519793147065</v>
+        <v>-30.21438595430791</v>
       </c>
       <c r="F41">
-        <v>6.834477415878522</v>
+        <v>6.485913666658935</v>
       </c>
       <c r="G41">
-        <v>-3.170748285398247</v>
+        <v>-5.257096607863373</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.813153239593799</v>
       </c>
       <c r="E42">
-        <v>-28.97105945194696</v>
+        <v>-28.35386467249355</v>
       </c>
       <c r="F42">
-        <v>6.468796282647486</v>
+        <v>6.135626913241525</v>
       </c>
       <c r="G42">
-        <v>-3.652192081150892</v>
+        <v>-5.680689186301447</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.609409853203509</v>
       </c>
       <c r="E43">
-        <v>-28.35528208485795</v>
+        <v>-29.11178178173532</v>
       </c>
       <c r="F43">
-        <v>6.494283490896821</v>
+        <v>6.583395942620381</v>
       </c>
       <c r="G43">
-        <v>-4.403135728466969</v>
+        <v>-6.961356523395839</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.422932590118</v>
       </c>
       <c r="E44">
-        <v>-28.32278575537891</v>
+        <v>-29.54447973740522</v>
       </c>
       <c r="F44">
-        <v>6.624348770279983</v>
+        <v>5.880567619715141</v>
       </c>
       <c r="G44">
-        <v>-3.570985128776194</v>
+        <v>-6.014031765746996</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.259235980036307</v>
       </c>
       <c r="E45">
-        <v>-28.2622083585783</v>
+        <v>-28.4494200025294</v>
       </c>
       <c r="F45">
-        <v>6.958356447497577</v>
+        <v>5.874487402978592</v>
       </c>
       <c r="G45">
-        <v>-4.738981879962373</v>
+        <v>-7.05512399190009</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.11876163557459</v>
       </c>
       <c r="E46">
-        <v>-27.00605948206463</v>
+        <v>-23.93901913462366</v>
       </c>
       <c r="F46">
-        <v>7.067011742987983</v>
+        <v>6.633041657804961</v>
       </c>
       <c r="G46">
-        <v>-4.932130987059087</v>
+        <v>-7.496976568316475</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.001639184942649</v>
       </c>
       <c r="E47">
-        <v>-26.95337521545939</v>
+        <v>-27.36764907462909</v>
       </c>
       <c r="F47">
-        <v>6.965354495316427</v>
+        <v>6.398744564862343</v>
       </c>
       <c r="G47">
-        <v>-4.019964518419694</v>
+        <v>-7.453024605527713</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.91051075067829</v>
       </c>
       <c r="E48">
-        <v>-25.39240569654141</v>
+        <v>-27.32358702253446</v>
       </c>
       <c r="F48">
-        <v>7.113236300799</v>
+        <v>6.037032968225523</v>
       </c>
       <c r="G48">
-        <v>-5.641645930965614</v>
+        <v>-4.870585114268582</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.837894621575039</v>
       </c>
       <c r="E49">
-        <v>-25.75860527564569</v>
+        <v>-26.00176168748754</v>
       </c>
       <c r="F49">
-        <v>6.820186421445426</v>
+        <v>6.535781384307466</v>
       </c>
       <c r="G49">
-        <v>-4.0251258799327</v>
+        <v>-6.300840061036499</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.782094991317235</v>
       </c>
       <c r="E50">
-        <v>-25.30966594794727</v>
+        <v>-24.23399487453529</v>
       </c>
       <c r="F50">
-        <v>7.458781479202787</v>
+        <v>6.678620089041796</v>
       </c>
       <c r="G50">
-        <v>-5.021960989692005</v>
+        <v>-7.63581489616126</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.739603077432751</v>
       </c>
       <c r="E51">
-        <v>-23.59807485506017</v>
+        <v>-23.35746344561062</v>
       </c>
       <c r="F51">
-        <v>7.012238433580074</v>
+        <v>6.560955469678542</v>
       </c>
       <c r="G51">
-        <v>-5.293902070095664</v>
+        <v>-6.583057927364338</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.704128897893902</v>
       </c>
       <c r="E52">
-        <v>-22.82623268824481</v>
+        <v>-23.03038988193262</v>
       </c>
       <c r="F52">
-        <v>7.939299185483918</v>
+        <v>6.839649741941603</v>
       </c>
       <c r="G52">
-        <v>-5.284721212172338</v>
+        <v>-7.495562361824355</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.676731987781199</v>
       </c>
       <c r="E53">
-        <v>-22.01682682953584</v>
+        <v>-23.2748595512367</v>
       </c>
       <c r="F53">
-        <v>7.063328821515136</v>
+        <v>6.768310741212509</v>
       </c>
       <c r="G53">
-        <v>-5.480350922767991</v>
+        <v>-7.851026937023679</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.655193708621105</v>
       </c>
       <c r="E54">
-        <v>-21.29540016384788</v>
+        <v>-21.457827469555</v>
       </c>
       <c r="F54">
-        <v>7.15762353971061</v>
+        <v>6.868843065951062</v>
       </c>
       <c r="G54">
-        <v>-5.396502587037941</v>
+        <v>-8.255260308261031</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.634290051534867</v>
       </c>
       <c r="E55">
-        <v>-20.7079167023588</v>
+        <v>-20.93194483999226</v>
       </c>
       <c r="F55">
-        <v>7.119366219579717</v>
+        <v>6.293308305099217</v>
       </c>
       <c r="G55">
-        <v>-4.989247210744341</v>
+        <v>-8.63196423061464</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.614631001224051</v>
       </c>
       <c r="E56">
-        <v>-21.63917473966617</v>
+        <v>-20.43254019795236</v>
       </c>
       <c r="F56">
-        <v>7.109049731945253</v>
+        <v>6.517358493269205</v>
       </c>
       <c r="G56">
-        <v>-5.591223399261628</v>
+        <v>-7.709940972410675</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.594338668840738</v>
       </c>
       <c r="E57">
-        <v>-19.64894664108711</v>
+        <v>-21.50681650136998</v>
       </c>
       <c r="F57">
-        <v>6.961101657070455</v>
+        <v>5.779039597358422</v>
       </c>
       <c r="G57">
-        <v>-6.347013410821004</v>
+        <v>-8.070993467925733</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.570950954059695</v>
       </c>
       <c r="E58">
-        <v>-19.49532721732491</v>
+        <v>-18.86392661490943</v>
       </c>
       <c r="F58">
-        <v>6.923256863906157</v>
+        <v>6.142550407994124</v>
       </c>
       <c r="G58">
-        <v>-5.859827477339332</v>
+        <v>-8.191535704355054</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.549696429614379</v>
       </c>
       <c r="E59">
-        <v>-18.8225816472194</v>
+        <v>-18.70642176044865</v>
       </c>
       <c r="F59">
-        <v>6.543177048479659</v>
+        <v>5.86651519509405</v>
       </c>
       <c r="G59">
-        <v>-7.009757822619208</v>
+        <v>-7.572687474579102</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.528131656110212</v>
       </c>
       <c r="E60">
-        <v>-18.19273883986257</v>
+        <v>-19.79593637890208</v>
       </c>
       <c r="F60">
-        <v>6.384688826771641</v>
+        <v>6.3278346584479</v>
       </c>
       <c r="G60">
-        <v>-7.336331241987621</v>
+        <v>-8.289421105916409</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.507602129837709</v>
       </c>
       <c r="E61">
-        <v>-18.09135536377885</v>
+        <v>-18.93625993023395</v>
       </c>
       <c r="F61">
-        <v>6.840648753029379</v>
+        <v>5.910286128657976</v>
       </c>
       <c r="G61">
-        <v>-6.553805837161889</v>
+        <v>-8.353473831978329</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.490887609561552</v>
       </c>
       <c r="E62">
-        <v>-17.45850564968092</v>
+        <v>-18.62686100060789</v>
       </c>
       <c r="F62">
-        <v>6.67344610624391</v>
+        <v>5.546997320486224</v>
       </c>
       <c r="G62">
-        <v>-6.817222303954111</v>
+        <v>-7.442505009208134</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.477677721558637</v>
       </c>
       <c r="E63">
-        <v>-16.50457354301715</v>
+        <v>-16.12251071946401</v>
       </c>
       <c r="F63">
-        <v>6.619257624222377</v>
+        <v>5.361096764684765</v>
       </c>
       <c r="G63">
-        <v>-6.050325357416013</v>
+        <v>-8.207518534571109</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.47090987570801</v>
       </c>
       <c r="E64">
-        <v>-15.54187431067452</v>
+        <v>-17.29593796127957</v>
       </c>
       <c r="F64">
-        <v>6.256994334895292</v>
+        <v>5.925990317880249</v>
       </c>
       <c r="G64">
-        <v>-6.856301652727097</v>
+        <v>-8.432820331728822</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.47367752832643</v>
       </c>
       <c r="E65">
-        <v>-15.53675260657185</v>
+        <v>-17.0598006841496</v>
       </c>
       <c r="F65">
-        <v>6.140088500073003</v>
+        <v>5.286846880902234</v>
       </c>
       <c r="G65">
-        <v>-7.206926426126241</v>
+        <v>-8.97581984393665</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.481339443883625</v>
       </c>
       <c r="E66">
-        <v>-15.3854698753976</v>
+        <v>-16.40616074588246</v>
       </c>
       <c r="F66">
-        <v>5.776574375967691</v>
+        <v>5.649981612737065</v>
       </c>
       <c r="G66">
-        <v>-6.689084039614675</v>
+        <v>-8.134960882227109</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.4968389444071</v>
       </c>
       <c r="E67">
-        <v>-16.22739470595566</v>
+        <v>-15.74515750887884</v>
       </c>
       <c r="F67">
-        <v>5.95587947050806</v>
+        <v>5.493917194049637</v>
       </c>
       <c r="G67">
-        <v>-7.287155574476223</v>
+        <v>-8.196756127856132</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.520086591655534</v>
       </c>
       <c r="E68">
-        <v>-15.77147699981142</v>
+        <v>-15.19589889648851</v>
       </c>
       <c r="F68">
-        <v>5.621202472429005</v>
+        <v>5.123549158053562</v>
       </c>
       <c r="G68">
-        <v>-6.412204720764052</v>
+        <v>-8.379431575735097</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.548283798459979</v>
       </c>
       <c r="E69">
-        <v>-14.86733999333599</v>
+        <v>-15.55739791957282</v>
       </c>
       <c r="F69">
-        <v>5.158804474716709</v>
+        <v>4.791781386293137</v>
       </c>
       <c r="G69">
-        <v>-7.150427072094162</v>
+        <v>-8.220771388449707</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.585752850985228</v>
       </c>
       <c r="E70">
-        <v>-15.58610844478145</v>
+        <v>-15.61913007724538</v>
       </c>
       <c r="F70">
-        <v>5.120451063967092</v>
+        <v>4.774147101022342</v>
       </c>
       <c r="G70">
-        <v>-6.101817567348379</v>
+        <v>-6.815000916958367</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.630600063051467</v>
       </c>
       <c r="E71">
-        <v>-14.55895091341364</v>
+        <v>-14.31024259243838</v>
       </c>
       <c r="F71">
-        <v>4.793229372513231</v>
+        <v>5.123090242512411</v>
       </c>
       <c r="G71">
-        <v>-5.095148636575419</v>
+        <v>-6.955046734337027</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.680511061023203</v>
       </c>
       <c r="E72">
-        <v>-14.49548887867015</v>
+        <v>-15.44413172769296</v>
       </c>
       <c r="F72">
-        <v>4.853537832906646</v>
+        <v>4.747447162895308</v>
       </c>
       <c r="G72">
-        <v>-6.082911168722859</v>
+        <v>-8.559144080545884</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.737850407573728</v>
       </c>
       <c r="E73">
-        <v>-14.81767169041986</v>
+        <v>-14.41439296614079</v>
       </c>
       <c r="F73">
-        <v>4.69516558263502</v>
+        <v>4.924532232796175</v>
       </c>
       <c r="G73">
-        <v>-6.189498369859861</v>
+        <v>-7.486427441002861</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.802052179175348</v>
       </c>
       <c r="E74">
-        <v>-13.72414484399564</v>
+        <v>-14.59267898782277</v>
       </c>
       <c r="F74">
-        <v>5.07371623183595</v>
+        <v>4.437457170154483</v>
       </c>
       <c r="G74">
-        <v>-5.0252947107964</v>
+        <v>-8.686186416884464</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.873320502203057</v>
       </c>
       <c r="E75">
-        <v>-13.57005898741065</v>
+        <v>-13.97809713787179</v>
       </c>
       <c r="F75">
-        <v>4.330128919243362</v>
+        <v>4.117677531447373</v>
       </c>
       <c r="G75">
-        <v>-5.387515321186622</v>
+        <v>-7.699244190126885</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.955554170823447</v>
       </c>
       <c r="E76">
-        <v>-13.59046429128921</v>
+        <v>-13.377802623415</v>
       </c>
       <c r="F76">
-        <v>4.212282059051493</v>
+        <v>4.086421572604942</v>
       </c>
       <c r="G76">
-        <v>-5.650055701822471</v>
+        <v>-8.188520261741925</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.043679123803294</v>
       </c>
       <c r="E77">
-        <v>-14.54947734578959</v>
+        <v>-13.9742660488613</v>
       </c>
       <c r="F77">
-        <v>3.871007942976541</v>
+        <v>3.753477519132542</v>
       </c>
       <c r="G77">
-        <v>-5.604463128253987</v>
+        <v>-7.531038929325071</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.138941227867914</v>
       </c>
       <c r="E78">
-        <v>-15.03588526742747</v>
+        <v>-16.20713884171935</v>
       </c>
       <c r="F78">
-        <v>4.274926515520803</v>
+        <v>3.931617929104576</v>
       </c>
       <c r="G78">
-        <v>-5.564763628606266</v>
+        <v>-7.253368836078621</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.241530760388265</v>
       </c>
       <c r="E79">
-        <v>-14.71025628695792</v>
+        <v>-16.18061556945642</v>
       </c>
       <c r="F79">
-        <v>4.409238006210715</v>
+        <v>4.066234258998718</v>
       </c>
       <c r="G79">
-        <v>-4.15080979054567</v>
+        <v>-7.499129049659471</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.348738120593275</v>
       </c>
       <c r="E80">
-        <v>-15.19769670066955</v>
+        <v>-16.57417618851504</v>
       </c>
       <c r="F80">
-        <v>4.192298523826357</v>
+        <v>4.062064257493025</v>
       </c>
       <c r="G80">
-        <v>-4.828930006571431</v>
+        <v>-6.521147838980736</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.463117881574918</v>
       </c>
       <c r="E81">
-        <v>-14.96662678595416</v>
+        <v>-16.22287528889601</v>
       </c>
       <c r="F81">
-        <v>4.19945396145174</v>
+        <v>3.67886315369278</v>
       </c>
       <c r="G81">
-        <v>-4.48910701454598</v>
+        <v>-6.238952941203812</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.584981072538467</v>
       </c>
       <c r="E82">
-        <v>-17.04767795923106</v>
+        <v>-18.75108609958631</v>
       </c>
       <c r="F82">
-        <v>4.003818431932581</v>
+        <v>3.339664926329243</v>
       </c>
       <c r="G82">
-        <v>-4.815939650417589</v>
+        <v>-6.605035549369499</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.709907982978457</v>
       </c>
       <c r="E83">
-        <v>-16.45208852926825</v>
+        <v>-18.15305582213336</v>
       </c>
       <c r="F83">
-        <v>3.839420637172991</v>
+        <v>3.657870666971034</v>
       </c>
       <c r="G83">
-        <v>-5.109707416634675</v>
+        <v>-7.076593024563537</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.842053040638918</v>
       </c>
       <c r="E84">
-        <v>-17.66859514431878</v>
+        <v>-18.29698883999315</v>
       </c>
       <c r="F84">
-        <v>3.641503783826522</v>
+        <v>3.249263534926928</v>
       </c>
       <c r="G84">
-        <v>-3.934012919670039</v>
+        <v>-6.211413648655392</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.98243392885214</v>
       </c>
       <c r="E85">
-        <v>-18.07722652487492</v>
+        <v>-20.31379908099724</v>
       </c>
       <c r="F85">
-        <v>3.439932173498901</v>
+        <v>3.694310549020185</v>
       </c>
       <c r="G85">
-        <v>-3.773725246491165</v>
+        <v>-5.385428464274814</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.1297493442098</v>
       </c>
       <c r="E86">
-        <v>-19.72964404790379</v>
+        <v>-20.69686722578008</v>
       </c>
       <c r="F86">
-        <v>3.659409773605436</v>
+        <v>3.594396186364119</v>
       </c>
       <c r="G86">
-        <v>-3.865707730467078</v>
+        <v>-5.82568308579175</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.29022397982237</v>
       </c>
       <c r="E87">
-        <v>-21.58390471440255</v>
+        <v>-22.40461817270868</v>
       </c>
       <c r="F87">
-        <v>3.700069359204447</v>
+        <v>3.676371424545159</v>
       </c>
       <c r="G87">
-        <v>-4.361523276650091</v>
+        <v>-5.428336998607673</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.46040613567782</v>
       </c>
       <c r="E88">
-        <v>-21.61645538556969</v>
+        <v>-23.42597472887266</v>
       </c>
       <c r="F88">
-        <v>3.257394789352808</v>
+        <v>3.521352405520064</v>
       </c>
       <c r="G88">
-        <v>-3.281082641556135</v>
+        <v>-5.603665791415042</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-10.64014181478427</v>
       </c>
       <c r="E89">
-        <v>-23.85022934475527</v>
+        <v>-25.6547084964877</v>
       </c>
       <c r="F89">
-        <v>3.101719703344697</v>
+        <v>2.585000684826421</v>
       </c>
       <c r="G89">
-        <v>-3.96402625327428</v>
+        <v>-5.618044104288529</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-10.83211667899653</v>
       </c>
       <c r="E90">
-        <v>-25.59639533669093</v>
+        <v>-27.86298261853609</v>
       </c>
       <c r="F90">
-        <v>2.719600447372507</v>
+        <v>3.32828647168439</v>
       </c>
       <c r="G90">
-        <v>-3.813779118067306</v>
+        <v>-4.622882417524541</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.03602748745327</v>
       </c>
       <c r="E91">
-        <v>-26.70183659822933</v>
+        <v>-28.62119407858836</v>
       </c>
       <c r="F91">
-        <v>2.968077533516247</v>
+        <v>2.913339015539255</v>
       </c>
       <c r="G91">
-        <v>-4.035304229210097</v>
+        <v>-5.272892408450539</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.25274101156676</v>
       </c>
       <c r="E92">
-        <v>-29.0872691519318</v>
+        <v>-29.17520758868675</v>
       </c>
       <c r="F92">
-        <v>2.782162067101537</v>
+        <v>2.225270543017097</v>
       </c>
       <c r="G92">
-        <v>-3.739213358128925</v>
+        <v>-5.497003122182173</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.48490346919054</v>
       </c>
       <c r="E93">
-        <v>-30.23390367728097</v>
+        <v>-31.91307995322117</v>
       </c>
       <c r="F93">
-        <v>3.019234190843533</v>
+        <v>2.060296204545158</v>
       </c>
       <c r="G93">
-        <v>-3.619543926634417</v>
+        <v>-6.417044522564233</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.72315987460159</v>
       </c>
       <c r="E94">
-        <v>-32.39974373364048</v>
+        <v>-32.45152456968119</v>
       </c>
       <c r="F94">
-        <v>2.640898917167332</v>
+        <v>1.777728486306608</v>
       </c>
       <c r="G94">
-        <v>-2.848817794536448</v>
+        <v>-4.757583124982865</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.97026003072924</v>
       </c>
       <c r="E95">
-        <v>-34.75570271426403</v>
+        <v>-35.81036393251742</v>
       </c>
       <c r="F95">
-        <v>2.457312819889294</v>
+        <v>2.167061165622375</v>
       </c>
       <c r="G95">
-        <v>-3.566647353874609</v>
+        <v>-5.149190355659473</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.22571337202181</v>
       </c>
       <c r="E96">
-        <v>-36.62553453863816</v>
+        <v>-35.80896010557504</v>
       </c>
       <c r="F96">
-        <v>2.302481011897233</v>
+        <v>1.559112388298985</v>
       </c>
       <c r="G96">
-        <v>-3.804516229604994</v>
+        <v>-5.16640364396032</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.48227983695465</v>
       </c>
       <c r="E97">
-        <v>-38.65483431095539</v>
+        <v>-39.89292136888947</v>
       </c>
       <c r="F97">
-        <v>2.352494522208656</v>
+        <v>1.213317042939553</v>
       </c>
       <c r="G97">
-        <v>-3.481739183580858</v>
+        <v>-5.878838875054754</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.74630425943649</v>
       </c>
       <c r="E98">
-        <v>-41.36120208181846</v>
+        <v>-39.74922836015209</v>
       </c>
       <c r="F98">
-        <v>2.208404982696099</v>
+        <v>1.675378723486312</v>
       </c>
       <c r="G98">
-        <v>-3.957887087736559</v>
+        <v>-7.105579335819672</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.00721790396429</v>
       </c>
       <c r="E99">
-        <v>-43.43490127754391</v>
+        <v>-42.99980096641293</v>
       </c>
       <c r="F99">
-        <v>2.051180849644752</v>
+        <v>1.646965721570289</v>
       </c>
       <c r="G99">
-        <v>-4.047073970943826</v>
+        <v>-6.599053882466632</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.2670971523942</v>
       </c>
       <c r="E100">
-        <v>-46.09725001681541</v>
+        <v>-45.66210215670735</v>
       </c>
       <c r="F100">
-        <v>2.127998672375962</v>
+        <v>0.7938814922060516</v>
       </c>
       <c r="G100">
-        <v>-4.843150820810065</v>
+        <v>-5.788569188732871</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.51155012526187</v>
       </c>
       <c r="E101">
-        <v>-47.90818903671979</v>
+        <v>-49.06825275173871</v>
       </c>
       <c r="F101">
-        <v>1.974641358360884</v>
+        <v>0.9801548133387709</v>
       </c>
       <c r="G101">
-        <v>-3.906033943432654</v>
+        <v>-6.080450252553275</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-13.76063159353772</v>
       </c>
       <c r="E102">
-        <v>-49.28098008248603</v>
+        <v>-50.34098716430547</v>
       </c>
       <c r="F102">
-        <v>1.892712508754401</v>
+        <v>1.569246635104834</v>
       </c>
       <c r="G102">
-        <v>-4.745987287991788</v>
+        <v>-6.196073937864989</v>
       </c>
     </row>
   </sheetData>
